--- a/erp-server/erp-server-wms/src/main/resources/excel/otherOutstockError.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/otherOutstockError.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27360" windowHeight="8235"/>
+    <workbookView windowWidth="27450" windowHeight="8235"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -228,7 +228,7 @@
     <t>{.type}</t>
   </si>
   <si>
-    <t>{.billDate}</t>
+    <t>{.billDateStr}</t>
   </si>
   <si>
     <t>{.warehouseName}</t>
@@ -255,7 +255,7 @@
     <t>{.skuNo}</t>
   </si>
   <si>
-    <t>{.actualQty}</t>
+    <t>{.actualQtyStr}</t>
   </si>
   <si>
     <t>{.warehouseLocation}</t>

--- a/erp-server/erp-server-wms/src/main/resources/excel/otherOutstockError.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/otherOutstockError.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27450" windowHeight="8235"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,58 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>业务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>类型</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>出库</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>类型</t>
+    </r>
+  </si>
+  <si>
+    <t>出库日期[不填默认今天]</t>
+  </si>
   <si>
     <r>
       <rPr>
@@ -49,11 +100,8 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>出库类型</t>
-    </r>
-  </si>
-  <si>
-    <t>出库日期[不填默认今天]</t>
+      <t>发货仓库</t>
+    </r>
   </si>
   <si>
     <r>
@@ -74,8 +122,11 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>发货仓库</t>
-    </r>
+      <t>库存方向</t>
+    </r>
+  </si>
+  <si>
+    <t>领料人</t>
   </si>
   <si>
     <r>
@@ -96,11 +147,8 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>库存方向</t>
-    </r>
-  </si>
-  <si>
-    <t>领料人</t>
+      <t>领料组织</t>
+    </r>
   </si>
   <si>
     <r>
@@ -121,7 +169,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>领料组织</t>
+      <t>领料部门</t>
     </r>
   </si>
   <si>
@@ -143,8 +191,11 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>领料部门</t>
-    </r>
+      <t>流程申请单</t>
+    </r>
+  </si>
+  <si>
+    <t>客户名称</t>
   </si>
   <si>
     <r>
@@ -165,11 +216,8 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>流程申请单</t>
-    </r>
-  </si>
-  <si>
-    <t>客户名称</t>
+      <t>SKU</t>
+    </r>
   </si>
   <si>
     <r>
@@ -190,28 +238,6 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>SKU</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>实发数量</t>
     </r>
   </si>
@@ -226,6 +252,9 @@
   </si>
   <si>
     <t>{.type}</t>
+  </si>
+  <si>
+    <t>{.outType}</t>
   </si>
   <si>
     <t>{.billDateStr}</t>
@@ -277,7 +306,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,6 +463,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1210,41 +1245,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="12.25" customWidth="1"/>
-    <col min="2" max="2" width="23.25" customWidth="1"/>
-    <col min="3" max="3" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="13.625" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="13.25" customWidth="1"/>
-    <col min="7" max="7" width="16.375" customWidth="1"/>
-    <col min="8" max="8" width="15.25" customWidth="1"/>
-    <col min="9" max="9" width="17.75" customWidth="1"/>
-    <col min="10" max="10" width="17.125" customWidth="1"/>
-    <col min="11" max="11" width="20.75" customWidth="1"/>
-    <col min="12" max="12" width="12.375" customWidth="1"/>
-    <col min="13" max="13" width="16.5" customWidth="1"/>
+    <col min="1" max="2" width="12.25" customWidth="1"/>
+    <col min="3" max="3" width="23.25" customWidth="1"/>
+    <col min="4" max="4" width="14.875" customWidth="1"/>
+    <col min="5" max="5" width="13.625" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="13.25" customWidth="1"/>
+    <col min="8" max="8" width="16.375" customWidth="1"/>
+    <col min="9" max="9" width="15.25" customWidth="1"/>
+    <col min="10" max="10" width="17.75" customWidth="1"/>
+    <col min="11" max="11" width="17.125" customWidth="1"/>
+    <col min="12" max="12" width="20.75" customWidth="1"/>
+    <col min="13" max="13" width="12.375" customWidth="1"/>
+    <col min="14" max="14" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1253,81 +1288,91 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 A3:A1048576">
+  <dataValidations count="3">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 B1 B3:B1048576"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E3:E1048576">
+      <formula1>"普通,退货"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A1048576">
       <formula1>"样品领用,KOL寄送,辅料包材,配件,报废,报损"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1 D3:D1048576">
-      <formula1>"普通,退货"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A2:A1048576" listDataValidation="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 

--- a/erp-server/erp-server-wms/src/main/resources/excel/otherOutstockError.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/otherOutstockError.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
-  <si>
-    <r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -56,6 +63,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -195,6 +209,12 @@
     </r>
   </si>
   <si>
+    <t>用途</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>客户名称</t>
   </si>
   <si>
@@ -245,6 +265,28 @@
     <t>仓位</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>出库类型</t>
+    </r>
+  </si>
+  <si>
     <t>出库备注</t>
   </si>
   <si>
@@ -278,6 +320,12 @@
     <t>{.processApplyCode}</t>
   </si>
   <si>
+    <t>{.usage}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
+  </si>
+  <si>
     <t>{.customerName}</t>
   </si>
   <si>
@@ -290,7 +338,7 @@
     <t>{.warehouseLocation}</t>
   </si>
   <si>
-    <t>{.remark}</t>
+    <t>{.detailRemark}</t>
   </si>
   <si>
     <t>{.errorMsg}</t>
@@ -1245,7 +1293,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="2" width="12.25" customWidth="1"/>
@@ -1256,14 +1304,15 @@
     <col min="7" max="7" width="13.25" customWidth="1"/>
     <col min="8" max="8" width="16.375" customWidth="1"/>
     <col min="9" max="9" width="15.25" customWidth="1"/>
-    <col min="10" max="10" width="17.75" customWidth="1"/>
-    <col min="11" max="11" width="17.125" customWidth="1"/>
-    <col min="12" max="12" width="20.75" customWidth="1"/>
-    <col min="13" max="13" width="12.375" customWidth="1"/>
-    <col min="14" max="14" width="16.5" customWidth="1"/>
+    <col min="10" max="12" width="17.75" customWidth="1"/>
+    <col min="13" max="13" width="17.125" customWidth="1"/>
+    <col min="14" max="14" width="20.75" customWidth="1"/>
+    <col min="15" max="15" width="19.75" customWidth="1"/>
+    <col min="16" max="16" width="15.125" customWidth="1"/>
+    <col min="17" max="17" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1294,72 +1343,90 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" t="s">
-        <v>29</v>
+      <c r="Q2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 B1 B3:B1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:B1 P1 B3:B1048576"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E3:E1048576">
       <formula1>"普通,退货"</formula1>
     </dataValidation>

--- a/erp-server/erp-server-wms/src/main/resources/excel/otherOutstockError.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/otherOutstockError.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <r>
       <rPr>
@@ -263,28 +263,6 @@
   </si>
   <si>
     <t>仓位</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>出库类型</t>
-    </r>
   </si>
   <si>
     <t>出库备注</t>
@@ -1293,7 +1271,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="2" width="12.25" customWidth="1"/>
@@ -1308,11 +1286,10 @@
     <col min="13" max="13" width="17.125" customWidth="1"/>
     <col min="14" max="14" width="20.75" customWidth="1"/>
     <col min="15" max="15" width="19.75" customWidth="1"/>
-    <col min="16" max="16" width="15.125" customWidth="1"/>
-    <col min="17" max="17" width="16.5" customWidth="1"/>
+    <col min="16" max="16" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1358,75 +1335,69 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>24</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>25</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>28</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>29</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>30</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>31</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>32</v>
-      </c>
-      <c r="P2" t="s">
-        <v>19</v>
       </c>
       <c r="Q2" t="s">
         <v>33</v>
-      </c>
-      <c r="R2" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:B1 P1 B3:B1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:B1 B3:B1048576"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E3:E1048576">
       <formula1>"普通,退货"</formula1>
     </dataValidation>
